--- a/posts/clima-economist/distr-normal.xlsx
+++ b/posts/clima-economist/distr-normal.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/34bf2af71bbc2e43/Documentos/GitHub/blog/posts/clima-economist/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\juanr\GitHub\blog\posts\clima-economist\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="319" documentId="8_{56F7861F-2369-4636-8BD1-46CD89C110AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AAB6ECDA-9F8A-495F-96C5-0D073BB885AA}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4996FB9E-A532-4934-8424-35BA6D69432A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31245" yWindow="2775" windowWidth="14055" windowHeight="11985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Inicio" sheetId="4" r:id="rId1"/>
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -214,7 +214,9 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
+    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{DC8118D0-CA35-4DD8-9022-4B615345FDA8}"/>
+  </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1454,6 +1456,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1461,7 +1464,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -2724,6 +2726,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -2731,7 +2734,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -3528,6 +3530,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -3535,7 +3538,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -4325,6 +4327,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -4332,7 +4335,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -5108,6 +5110,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -5115,7 +5118,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -9107,8 +9109,8 @@
       </cdr:nvGrpSpPr>
       <cdr:grpSpPr>
         <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="1974053" y="2051636"/>
-          <a:ext cx="573783" cy="110680"/>
+          <a:off x="1901113" y="1909471"/>
+          <a:ext cx="552582" cy="103010"/>
           <a:chOff x="1951536" y="1734927"/>
           <a:chExt cx="569193" cy="111672"/>
         </a:xfrm>
@@ -9789,8 +9791,8 @@
       </cdr:nvGrpSpPr>
       <cdr:grpSpPr>
         <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="1998209" y="2015450"/>
-          <a:ext cx="573829" cy="110266"/>
+          <a:off x="1924377" y="1887345"/>
+          <a:ext cx="552625" cy="103257"/>
           <a:chOff x="0" y="0"/>
           <a:chExt cx="569193" cy="111672"/>
         </a:xfrm>
@@ -10501,9 +10503,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -10541,7 +10543,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -10647,7 +10649,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -10789,7 +10791,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -10801,12 +10803,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I40"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="3" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="12.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" s="13" t="s">
         <v>4</v>
       </c>
@@ -10827,7 +10829,7 @@
       </c>
       <c r="I1" s="17"/>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="15" t="s">
         <v>0</v>
       </c>
@@ -10845,7 +10847,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
@@ -10866,7 +10868,7 @@
       </c>
       <c r="I3" s="10"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="5">
         <v>-4</v>
       </c>
@@ -10903,7 +10905,7 @@
         <v>1.4870025084987264E-5</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" s="5">
         <v>-3.75</v>
       </c>
@@ -10940,7 +10942,7 @@
         <v>3.9177298040827269E-5</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" s="5">
         <v>-3.5</v>
       </c>
@@ -10977,7 +10979,7 @@
         <v>9.6964743893973346E-5</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" s="5">
         <v>-3.25</v>
       </c>
@@ -11014,7 +11016,7 @@
         <v>2.2544978414441866E-4</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" s="5">
         <v>-3</v>
       </c>
@@ -11051,7 +11053,7 @@
         <v>4.9242760132644527E-4</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" s="5">
         <v>-2.75</v>
       </c>
@@ -11088,7 +11090,7 @@
         <v>1.0103958335101171E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" s="5">
         <v>-2.5</v>
       </c>
@@ -11125,7 +11127,7 @@
         <v>1.9475889437298376E-3</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" s="5">
         <v>-2.25</v>
       </c>
@@ -11162,7 +11164,7 @@
         <v>3.5266279817408241E-3</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" s="5">
         <v>-2</v>
       </c>
@@ -11199,7 +11201,7 @@
         <v>5.9989962792431177E-3</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" s="5">
         <v>-1.75</v>
       </c>
@@ -11236,7 +11238,7 @@
         <v>9.5863687585012805E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" s="5">
         <v>-1.5</v>
       </c>
@@ -11273,7 +11275,7 @@
         <v>1.439084396287686E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" s="5">
         <v>-1.25</v>
       </c>
@@ -11310,7 +11312,7 @@
         <v>2.0294342821002436E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" s="5">
         <v>-1</v>
       </c>
@@ -11347,7 +11349,7 @@
         <v>2.6885636057682596E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" s="5">
         <v>-0.75</v>
       </c>
@@ -11384,7 +11386,7 @@
         <v>3.3459714683867159E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" s="5">
         <v>-0.5</v>
       </c>
@@ -11421,7 +11423,7 @@
         <v>3.911836964047772E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" s="5">
         <v>-0.25</v>
       </c>
@@ -11458,7 +11460,7 @@
         <v>4.2963124089205468E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" s="5">
         <v>0</v>
       </c>
@@ -11495,7 +11497,7 @@
         <v>4.4326920044603632E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21" s="5">
         <v>0.25</v>
       </c>
@@ -11532,7 +11534,7 @@
         <v>4.2963124089205468E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" s="5">
         <v>0.5</v>
       </c>
@@ -11569,7 +11571,7 @@
         <v>3.911836964047772E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23" s="5">
         <v>0.75</v>
       </c>
@@ -11606,7 +11608,7 @@
         <v>3.3459714683867159E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A24" s="5">
         <v>1</v>
       </c>
@@ -11643,7 +11645,7 @@
         <v>2.6885636057682596E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A25" s="5">
         <v>1.25</v>
       </c>
@@ -11680,7 +11682,7 @@
         <v>2.0294342821002436E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A26" s="5">
         <v>1.5</v>
       </c>
@@ -11717,7 +11719,7 @@
         <v>1.439084396287686E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27" s="5">
         <v>1.75</v>
       </c>
@@ -11754,7 +11756,7 @@
         <v>9.5863687585012805E-3</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A28" s="5">
         <v>2</v>
       </c>
@@ -11791,7 +11793,7 @@
         <v>5.9989962792431177E-3</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A29" s="5">
         <v>2.25</v>
       </c>
@@ -11828,7 +11830,7 @@
         <v>3.5266279817408241E-3</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A30" s="5">
         <v>2.5</v>
       </c>
@@ -11865,7 +11867,7 @@
         <v>1.9475889437298376E-3</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A31" s="5">
         <v>2.75</v>
       </c>
@@ -11902,7 +11904,7 @@
         <v>1.0103958335101171E-3</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A32" s="5">
         <v>3</v>
       </c>
@@ -11939,7 +11941,7 @@
         <v>4.9242760132644527E-4</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A33" s="5">
         <v>3.25</v>
       </c>
@@ -11976,7 +11978,7 @@
         <v>2.2544978414441866E-4</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A34" s="5">
         <v>3.5</v>
       </c>
@@ -12013,7 +12015,7 @@
         <v>9.6964743893973346E-5</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A35" s="5">
         <v>3.75</v>
       </c>
@@ -12050,7 +12052,7 @@
         <v>3.9177298040827269E-5</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A36" s="9">
         <v>4</v>
       </c>
@@ -12087,7 +12089,7 @@
         <v>1.4870025084987264E-5</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A37" s="11" t="s">
         <v>2</v>
       </c>
@@ -12120,7 +12122,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A38" s="13" t="s">
         <v>2</v>
       </c>
@@ -12157,7 +12159,7 @@
         <v>4.4326920044603632E-2</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A40" s="8" t="s">
         <v>3</v>
       </c>
@@ -12183,12 +12185,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:I40"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="3" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="12.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -12206,7 +12208,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
@@ -12224,7 +12226,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="5">
         <v>-4</v>
       </c>
@@ -12261,7 +12263,7 @@
         <v>1.4870025084987264E-5</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" s="5">
         <v>-3.75</v>
       </c>
@@ -12298,7 +12300,7 @@
         <v>3.9177298040827269E-5</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" s="5">
         <v>-3.5</v>
       </c>
@@ -12335,7 +12337,7 @@
         <v>9.6964743893973346E-5</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" s="5">
         <v>-3.25</v>
       </c>
@@ -12372,7 +12374,7 @@
         <v>2.2544978414441866E-4</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" s="5">
         <v>-3</v>
       </c>
@@ -12409,7 +12411,7 @@
         <v>4.9242760132644527E-4</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" s="5">
         <v>-2.75</v>
       </c>
@@ -12446,7 +12448,7 @@
         <v>1.0103958335101171E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" s="5">
         <v>-2.5</v>
       </c>
@@ -12483,7 +12485,7 @@
         <v>1.9475889437298376E-3</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" s="5">
         <v>-2.25</v>
       </c>
@@ -12520,7 +12522,7 @@
         <v>3.5266279817408241E-3</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" s="5">
         <v>-2</v>
       </c>
@@ -12557,7 +12559,7 @@
         <v>5.9989962792431177E-3</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" s="5">
         <v>-1.75</v>
       </c>
@@ -12594,7 +12596,7 @@
         <v>9.5863687585012805E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" s="5">
         <v>-1.5</v>
       </c>
@@ -12631,7 +12633,7 @@
         <v>1.439084396287686E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" s="5">
         <v>-1.25</v>
       </c>
@@ -12668,7 +12670,7 @@
         <v>2.0294342821002436E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" s="5">
         <v>-1</v>
       </c>
@@ -12705,7 +12707,7 @@
         <v>2.6885636057682596E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" s="5">
         <v>-0.75</v>
       </c>
@@ -12742,7 +12744,7 @@
         <v>3.3459714683867159E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" s="5">
         <v>-0.5</v>
       </c>
@@ -12779,7 +12781,7 @@
         <v>3.911836964047772E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" s="5">
         <v>-0.25</v>
       </c>
@@ -12816,7 +12818,7 @@
         <v>4.2963124089205468E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" s="5">
         <v>0</v>
       </c>
@@ -12853,7 +12855,7 @@
         <v>4.4326920044603632E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21" s="5">
         <v>0.25</v>
       </c>
@@ -12890,7 +12892,7 @@
         <v>4.2963124089205468E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" s="5">
         <v>0.5</v>
       </c>
@@ -12927,7 +12929,7 @@
         <v>3.911836964047772E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23" s="5">
         <v>0.75</v>
       </c>
@@ -12964,7 +12966,7 @@
         <v>3.3459714683867159E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A24" s="5">
         <v>1</v>
       </c>
@@ -13001,7 +13003,7 @@
         <v>2.6885636057682596E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A25" s="5">
         <v>1.25</v>
       </c>
@@ -13038,7 +13040,7 @@
         <v>2.0294342821002436E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A26" s="5">
         <v>1.5</v>
       </c>
@@ -13075,7 +13077,7 @@
         <v>1.439084396287686E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27" s="5">
         <v>1.75</v>
       </c>
@@ -13112,7 +13114,7 @@
         <v>9.5863687585012805E-3</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A28" s="5">
         <v>2</v>
       </c>
@@ -13149,7 +13151,7 @@
         <v>5.9989962792431177E-3</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A29" s="5">
         <v>2.25</v>
       </c>
@@ -13186,7 +13188,7 @@
         <v>3.5266279817408241E-3</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A30" s="5">
         <v>2.5</v>
       </c>
@@ -13223,7 +13225,7 @@
         <v>1.9475889437298376E-3</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A31" s="5">
         <v>2.75</v>
       </c>
@@ -13260,7 +13262,7 @@
         <v>1.0103958335101171E-3</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A32" s="5">
         <v>3</v>
       </c>
@@ -13297,7 +13299,7 @@
         <v>4.9242760132644527E-4</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A33" s="5">
         <v>3.25</v>
       </c>
@@ -13334,7 +13336,7 @@
         <v>2.2544978414441866E-4</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A34" s="5">
         <v>3.5</v>
       </c>
@@ -13371,7 +13373,7 @@
         <v>9.6964743893973346E-5</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A35" s="5">
         <v>3.75</v>
       </c>
@@ -13408,7 +13410,7 @@
         <v>3.9177298040827269E-5</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A36" s="5">
         <v>4</v>
       </c>
@@ -13445,7 +13447,7 @@
         <v>1.4870025084987264E-5</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A37" s="4" t="s">
         <v>2</v>
       </c>
@@ -13478,7 +13480,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A38" s="4" t="s">
         <v>2</v>
       </c>
@@ -13515,7 +13517,7 @@
         <v>4.4326920044603632E-2</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A40" s="8" t="s">
         <v>3</v>
       </c>
